--- a/artfynd/A 7457-2023 artfynd.xlsx
+++ b/artfynd/A 7457-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 7457-2023 artfynd.xlsx
+++ b/artfynd/A 7457-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1838,6 +1838,115 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128702142</v>
+      </c>
+      <c r="B13" t="n">
+        <v>86726</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>459</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Frygisk spindling</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cortinarius phrygianus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Vågen, Ö om, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>505371</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7017637</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lars-Olof Grund</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lars-Olof Grund</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7457-2023 artfynd.xlsx
+++ b/artfynd/A 7457-2023 artfynd.xlsx
@@ -1844,7 +1844,7 @@
         <v>128702142</v>
       </c>
       <c r="B13" t="n">
-        <v>86726</v>
+        <v>86728</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 7457-2023 artfynd.xlsx
+++ b/artfynd/A 7457-2023 artfynd.xlsx
@@ -1844,7 +1844,7 @@
         <v>128702142</v>
       </c>
       <c r="B13" t="n">
-        <v>86728</v>
+        <v>86755</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 7457-2023 artfynd.xlsx
+++ b/artfynd/A 7457-2023 artfynd.xlsx
@@ -1844,7 +1844,7 @@
         <v>128702142</v>
       </c>
       <c r="B13" t="n">
-        <v>86755</v>
+        <v>86759</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 7457-2023 artfynd.xlsx
+++ b/artfynd/A 7457-2023 artfynd.xlsx
@@ -1844,7 +1844,7 @@
         <v>128702142</v>
       </c>
       <c r="B13" t="n">
-        <v>86759</v>
+        <v>86763</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 7457-2023 artfynd.xlsx
+++ b/artfynd/A 7457-2023 artfynd.xlsx
@@ -1844,7 +1844,7 @@
         <v>128702142</v>
       </c>
       <c r="B13" t="n">
-        <v>86763</v>
+        <v>86768</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 7457-2023 artfynd.xlsx
+++ b/artfynd/A 7457-2023 artfynd.xlsx
@@ -1844,7 +1844,7 @@
         <v>128702142</v>
       </c>
       <c r="B13" t="n">
-        <v>86775</v>
+        <v>86778</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 7457-2023 artfynd.xlsx
+++ b/artfynd/A 7457-2023 artfynd.xlsx
@@ -1844,7 +1844,7 @@
         <v>128702142</v>
       </c>
       <c r="B13" t="n">
-        <v>86778</v>
+        <v>86781</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 7457-2023 artfynd.xlsx
+++ b/artfynd/A 7457-2023 artfynd.xlsx
@@ -1844,7 +1844,7 @@
         <v>128702142</v>
       </c>
       <c r="B13" t="n">
-        <v>86781</v>
+        <v>86785</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 7457-2023 artfynd.xlsx
+++ b/artfynd/A 7457-2023 artfynd.xlsx
@@ -2147,7 +2147,7 @@
         <v>130069578</v>
       </c>
       <c r="B16" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 7457-2023 artfynd.xlsx
+++ b/artfynd/A 7457-2023 artfynd.xlsx
@@ -1953,7 +1953,7 @@
         <v>130069582</v>
       </c>
       <c r="B14" t="n">
-        <v>86891</v>
+        <v>86978</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>130069581</v>
       </c>
       <c r="B15" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>130069578</v>
       </c>
       <c r="B16" t="n">
-        <v>92596</v>
+        <v>92683</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 7457-2023 artfynd.xlsx
+++ b/artfynd/A 7457-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113258592</v>
+        <v>128702142</v>
       </c>
       <c r="B2" t="n">
-        <v>91617</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>459</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Frygisk spindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius phrygianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skogar vid Rödmossaflon, Jmt</t>
+          <t>Vågen, Ö om, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505374</v>
+        <v>505371</v>
       </c>
       <c r="R2" t="n">
-        <v>7017577</v>
+        <v>7017637</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,72 +765,64 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Lars-Olof Grund</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2023</t>
-        </is>
-      </c>
+          <t>Lars-Olof Grund</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113258624</v>
+        <v>130069582</v>
       </c>
       <c r="B3" t="n">
-        <v>91263</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87145</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>459</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Frygisk spindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius phrygianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skogar vid Rödmossaflon, Jmt</t>
+          <t>Rödmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505392</v>
+        <v>505356</v>
       </c>
       <c r="R3" t="n">
-        <v>7017554</v>
+        <v>7017618</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,12 +849,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,66 +869,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2023</t>
-        </is>
-      </c>
+          <t>Väg och Miljö AB, Lars-Olof Grund</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113258600</v>
+        <v>111814073</v>
       </c>
       <c r="B4" t="n">
-        <v>91590</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1968</v>
+        <v>504</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skogar vid Rödmossaflon, Jmt</t>
+          <t>Skog väster om Rödmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505377</v>
+        <v>505336</v>
       </c>
       <c r="R4" t="n">
-        <v>7017580</v>
+        <v>7017612</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +946,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2023-08-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>I vägkanten</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,37 +987,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113258583</v>
+        <v>113258652</v>
       </c>
       <c r="B5" t="n">
-        <v>87189</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4412</v>
+        <v>504</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505444</v>
+        <v>505329</v>
       </c>
       <c r="R5" t="n">
-        <v>7017576</v>
+        <v>7017627</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,37 +1088,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113258599</v>
+        <v>113258657</v>
       </c>
       <c r="B6" t="n">
-        <v>91232</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4745</v>
+        <v>504</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505384</v>
+        <v>505334</v>
       </c>
       <c r="R6" t="n">
-        <v>7017567</v>
+        <v>7017621</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,12 +1192,7 @@
         <v>113258651</v>
       </c>
       <c r="B7" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,37 +1290,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113258649</v>
+        <v>113258659</v>
       </c>
       <c r="B8" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90692</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1599</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällfotad musseron</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma olivaceotinctum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1325,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505402</v>
+        <v>505429</v>
       </c>
       <c r="R8" t="n">
-        <v>7017633</v>
+        <v>7017497</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,12 +1363,18 @@
           <t>2023-09-05</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Antingen fjällfotad musseron eller svartfjällig musseron.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1417,15 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113258635</v>
+        <v>113258600</v>
       </c>
       <c r="B9" t="n">
-        <v>87189</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1433,21 +1408,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4412</v>
+        <v>1968</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1432,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505538</v>
+        <v>505377</v>
       </c>
       <c r="R9" t="n">
-        <v>7017614</v>
+        <v>7017580</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,50 +1498,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113258619</v>
+        <v>130069580</v>
       </c>
       <c r="B10" t="n">
-        <v>91617</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>1968</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skogar vid Rödmossaflon, Jmt</t>
+          <t>Rödmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505353</v>
+        <v>505346</v>
       </c>
       <c r="R10" t="n">
-        <v>7017638</v>
+        <v>7017694</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,12 +1563,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1613,66 +1583,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2023</t>
-        </is>
-      </c>
+          <t>Väg och Miljö AB, Lars-Olof Grund</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113258654</v>
+        <v>111814408</v>
       </c>
       <c r="B11" t="n">
-        <v>91610</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6003298</v>
+        <v>4366</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ruttaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum illudens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Maas Geest.) Nitare</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skogar vid Rödmossaflon, Jmt</t>
+          <t>Skog väster om Rödmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>505349</v>
+        <v>505374</v>
       </c>
       <c r="R11" t="n">
-        <v>7017636</v>
+        <v>7017566</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,12 +1660,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Tallvarianten</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,37 +1701,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113258656</v>
+        <v>113258592</v>
       </c>
       <c r="B12" t="n">
-        <v>87175</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4405</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1736,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505417</v>
+        <v>505374</v>
       </c>
       <c r="R12" t="n">
-        <v>7017608</v>
+        <v>7017577</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128702142</v>
+        <v>113258619</v>
       </c>
       <c r="B13" t="n">
-        <v>86785</v>
+        <v>93209</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,48 +1813,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>459</v>
+        <v>4366</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Frygisk spindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius phrygianus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vågen, Ö om, Jmt</t>
+          <t>Skogar vid Rödmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505371</v>
+        <v>505353</v>
       </c>
       <c r="R13" t="n">
-        <v>7017637</v>
+        <v>7017638</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1917,12 +1867,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1931,64 +1881,67 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lars-Olof Grund</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lars-Olof Grund</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130069582</v>
+        <v>113258656</v>
       </c>
       <c r="B14" t="n">
-        <v>86978</v>
+        <v>89143</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>459</v>
+        <v>4405</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Frygisk spindling</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius phrygianus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rödmossaflon, Jmt</t>
+          <t>Skogar vid Rödmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505356</v>
+        <v>505417</v>
       </c>
       <c r="R14" t="n">
-        <v>7017618</v>
+        <v>7017608</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2015,12 +1968,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2035,22 +1988,26 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Lars-Olof Grund</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130069581</v>
+        <v>113258583</v>
       </c>
       <c r="B15" t="n">
-        <v>79180</v>
+        <v>89156</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2058,34 +2015,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rödmossaflon, Jmt</t>
+          <t>Skogar vid Rödmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>505420</v>
+        <v>505444</v>
       </c>
       <c r="R15" t="n">
-        <v>7017611</v>
+        <v>7017576</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,12 +2069,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2132,57 +2089,61 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Lars-Olof Grund</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130069578</v>
+        <v>113258635</v>
       </c>
       <c r="B16" t="n">
-        <v>92683</v>
+        <v>89156</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4769</v>
+        <v>4412</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rödmossaflon, Jmt</t>
+          <t>Skogar vid Rödmossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505467</v>
+        <v>505538</v>
       </c>
       <c r="R16" t="n">
-        <v>7017558</v>
+        <v>7017614</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2209,12 +2170,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2229,15 +2190,1308 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>113258599</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92841</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Skogar vid Rödmossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>505384</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7017567</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>113258620</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92841</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Skogar vid Rödmossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>505332</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7017616</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>113258616</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Skogar vid Rödmossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>505360</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7017597</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>113258624</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Skogar vid Rödmossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>505392</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7017554</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130069577</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Rödmossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>505344</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7017678</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
           <t>Väg och Miljö AB</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
+      <c r="AX21" t="inlineStr">
         <is>
           <t>Väg och Miljö AB, Lars-Olof Grund</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130069578</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Rödmossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>505467</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7017558</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Lars-Olof Grund</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>113258594</v>
+      </c>
+      <c r="B23" t="n">
+        <v>85065</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5589</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Rödbrun klubbdyna</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Trichoderma nybergianum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Skogar vid Rödmossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>505429</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7017497</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>113258649</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Skogar vid Rödmossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>505402</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7017633</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130069581</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Rödmossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>505420</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7017611</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Lars-Olof Grund</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130069584</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Rödmossaflom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>505344</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7017678</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Lars-Olof Grund, Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>113258654</v>
+      </c>
+      <c r="B27" t="n">
+        <v>93202</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6003298</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Ruttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hydnellum illudens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Maas Geest.) Nitare</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Skogar vid Rödmossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>505349</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7017636</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>113258626</v>
+      </c>
+      <c r="B28" t="n">
+        <v>93211</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6047725</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Rödfläckig zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Skogar vid Rödmossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>505329</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7017640</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>113258653</v>
+      </c>
+      <c r="B29" t="n">
+        <v>93211</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6047725</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Rödfläckig zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Skogar vid Rödmossaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>505330</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7017663</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7457-2023 artfynd.xlsx
+++ b/artfynd/A 7457-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128702142</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130069582</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111814073</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113258652</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1186,6 +1211,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113258657</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1287,6 +1317,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113258651</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1394,6 +1429,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113258659</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1495,6 +1535,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113258600</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1592,6 +1637,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130069580</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1698,6 +1748,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111814408</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1799,6 +1854,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113258592</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1900,6 +1960,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113258619</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2001,6 +2066,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113258656</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2102,6 +2172,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113258583</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2203,6 +2278,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113258635</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2304,6 +2384,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113258599</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2405,6 +2490,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113258620</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2506,6 +2596,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113258616</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2607,6 +2702,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113258624</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2704,6 +2804,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130069577</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2801,6 +2906,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130069578</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2902,6 +3012,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113258594</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3003,6 +3118,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113258649</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3100,6 +3220,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130069581</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3197,6 +3322,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130069584</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3298,6 +3428,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113258654</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3395,6 +3530,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113258626</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3492,8 +3632,43 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113258653</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>